--- a/Team-Data/2013-14/12-16-2013-14.xlsx
+++ b/Team-Data/2013-14/12-16-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,61 +728,61 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F2" t="n">
         <v>12</v>
       </c>
       <c r="G2" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="H2" t="n">
         <v>48.2</v>
       </c>
       <c r="I2" t="n">
-        <v>37.9</v>
+        <v>37.6</v>
       </c>
       <c r="J2" t="n">
-        <v>81.90000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="K2" t="n">
-        <v>0.462</v>
+        <v>0.461</v>
       </c>
       <c r="L2" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="N2" t="n">
-        <v>0.368</v>
+        <v>0.366</v>
       </c>
       <c r="O2" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="P2" t="n">
-        <v>21.2</v>
+        <v>21.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.753</v>
+        <v>0.75</v>
       </c>
       <c r="R2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="S2" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="T2" t="n">
-        <v>40.8</v>
+        <v>40.6</v>
       </c>
       <c r="U2" t="n">
-        <v>24.8</v>
+        <v>24.4</v>
       </c>
       <c r="V2" t="n">
-        <v>15</v>
+        <v>15.3</v>
       </c>
       <c r="W2" t="n">
         <v>8.4</v>
@@ -730,64 +797,64 @@
         <v>18.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>100.2</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AE2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF2" t="n">
         <v>12</v>
       </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
         <v>21</v>
       </c>
       <c r="AI2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AJ2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AK2" t="n">
         <v>8</v>
       </c>
       <c r="AL2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM2" t="n">
         <v>10</v>
       </c>
       <c r="AN2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AQ2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS2" t="n">
         <v>14</v>
       </c>
       <c r="AT2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU2" t="n">
         <v>2</v>
@@ -796,10 +863,10 @@
         <v>15</v>
       </c>
       <c r="AW2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AY2" t="n">
         <v>9</v>
@@ -811,10 +878,10 @@
         <v>24</v>
       </c>
       <c r="BB2" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC2" t="n">
         <v>15</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>14</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-16-2013-14</t>
+          <t>2013-12-16</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
         <v>14</v>
       </c>
       <c r="G3" t="n">
-        <v>0.462</v>
+        <v>0.44</v>
       </c>
       <c r="H3" t="n">
         <v>48</v>
@@ -861,76 +928,76 @@
         <v>36.3</v>
       </c>
       <c r="J3" t="n">
-        <v>80.3</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.452</v>
+        <v>0.453</v>
       </c>
       <c r="L3" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="O3" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="P3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.763</v>
+      </c>
+      <c r="R3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>31</v>
+      </c>
+      <c r="T3" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="V3" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="W3" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="X3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="AA3" t="n">
         <v>18.6</v>
       </c>
-      <c r="N3" t="n">
-        <v>0.358</v>
-      </c>
-      <c r="O3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="P3" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.764</v>
-      </c>
-      <c r="R3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="S3" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="T3" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="U3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="V3" t="n">
-        <v>16</v>
-      </c>
-      <c r="W3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="X3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>18.7</v>
-      </c>
       <c r="AB3" t="n">
-        <v>95</v>
+        <v>94.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.8</v>
+        <v>-1</v>
       </c>
       <c r="AD3" t="n">
         <v>2</v>
       </c>
       <c r="AE3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH3" t="n">
         <v>24</v>
@@ -945,31 +1012,31 @@
         <v>12</v>
       </c>
       <c r="AL3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AN3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO3" t="n">
         <v>25</v>
       </c>
       <c r="AP3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ3" t="n">
         <v>13</v>
       </c>
       <c r="AR3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AS3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AU3" t="n">
         <v>30</v>
@@ -978,19 +1045,19 @@
         <v>24</v>
       </c>
       <c r="AW3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AX3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AY3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
         <v>20</v>
       </c>
       <c r="BA3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BB3" t="n">
         <v>23</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-16-2013-14</t>
+          <t>2013-12-16</t>
         </is>
       </c>
     </row>
@@ -1025,88 +1092,88 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="n">
         <v>15</v>
       </c>
       <c r="G4" t="n">
-        <v>0.375</v>
+        <v>0.348</v>
       </c>
       <c r="H4" t="n">
         <v>48.4</v>
       </c>
       <c r="I4" t="n">
-        <v>35</v>
+        <v>34.4</v>
       </c>
       <c r="J4" t="n">
-        <v>78.59999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="K4" t="n">
-        <v>0.445</v>
+        <v>0.438</v>
       </c>
       <c r="L4" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="M4" t="n">
-        <v>19</v>
+        <v>18.3</v>
       </c>
       <c r="N4" t="n">
-        <v>0.37</v>
+        <v>0.351</v>
       </c>
       <c r="O4" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="P4" t="n">
         <v>26.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.754</v>
+        <v>0.762</v>
       </c>
       <c r="R4" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="S4" t="n">
-        <v>31.2</v>
+        <v>30.9</v>
       </c>
       <c r="T4" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="U4" t="n">
-        <v>19.9</v>
+        <v>19.3</v>
       </c>
       <c r="V4" t="n">
-        <v>14.7</v>
+        <v>14.4</v>
       </c>
       <c r="W4" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="X4" t="n">
         <v>4</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>96.8</v>
+        <v>95.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>-4.5</v>
+        <v>-6.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AE4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AF4" t="n">
         <v>24</v>
@@ -1115,25 +1182,25 @@
         <v>24</v>
       </c>
       <c r="AH4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ4" t="n">
         <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL4" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AM4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AN4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AO4" t="n">
         <v>5</v>
@@ -1142,31 +1209,31 @@
         <v>5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AR4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AS4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AT4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AV4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AW4" t="n">
         <v>27</v>
       </c>
       <c r="AX4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ4" t="n">
         <v>28</v>
@@ -1178,7 +1245,7 @@
         <v>22</v>
       </c>
       <c r="BC4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-16-2013-14</t>
+          <t>2013-12-16</t>
         </is>
       </c>
     </row>
@@ -1285,16 +1352,16 @@
         <v>-2.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AE5" t="n">
         <v>18</v>
       </c>
       <c r="AF5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG5" t="n">
         <v>19</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>20</v>
       </c>
       <c r="AH5" t="n">
         <v>24</v>
@@ -1348,7 +1415,7 @@
         <v>9</v>
       </c>
       <c r="AY5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ5" t="n">
         <v>5</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-16-2013-14</t>
+          <t>2013-12-16</t>
         </is>
       </c>
     </row>
@@ -1389,70 +1456,70 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E6" t="n">
         <v>9</v>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>0.391</v>
+        <v>0.409</v>
       </c>
       <c r="H6" t="n">
         <v>48.9</v>
       </c>
       <c r="I6" t="n">
-        <v>34.2</v>
+        <v>34.5</v>
       </c>
       <c r="J6" t="n">
-        <v>81.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="K6" t="n">
-        <v>0.417</v>
+        <v>0.42</v>
       </c>
       <c r="L6" t="n">
         <v>5.3</v>
       </c>
       <c r="M6" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.322</v>
+        <v>0.324</v>
       </c>
       <c r="O6" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="P6" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.783</v>
+        <v>0.781</v>
       </c>
       <c r="R6" t="n">
-        <v>12.6</v>
+        <v>12.9</v>
       </c>
       <c r="S6" t="n">
-        <v>33.3</v>
+        <v>33</v>
       </c>
       <c r="T6" t="n">
         <v>45.9</v>
       </c>
       <c r="U6" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="V6" t="n">
-        <v>16.1</v>
+        <v>16.6</v>
       </c>
       <c r="W6" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="X6" t="n">
         <v>4.9</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="Z6" t="n">
         <v>20</v>
@@ -1461,31 +1528,31 @@
         <v>21.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>91.2</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="AC6" t="n">
         <v>-1.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AE6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF6" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AG6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AH6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AK6" t="n">
         <v>28</v>
@@ -1506,7 +1573,7 @@
         <v>18</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR6" t="n">
         <v>6</v>
@@ -1521,7 +1588,7 @@
         <v>15</v>
       </c>
       <c r="AV6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AW6" t="n">
         <v>29</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-16-2013-14</t>
+          <t>2013-12-16</t>
         </is>
       </c>
     </row>
@@ -1649,16 +1716,16 @@
         <v>-5.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AE7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH7" t="n">
         <v>6</v>
@@ -1667,13 +1734,13 @@
         <v>25</v>
       </c>
       <c r="AJ7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK7" t="n">
         <v>26</v>
       </c>
       <c r="AL7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM7" t="n">
         <v>20</v>
@@ -1682,13 +1749,13 @@
         <v>18</v>
       </c>
       <c r="AO7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP7" t="n">
         <v>21</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="AQ7" t="n">
         <v>20</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>19</v>
       </c>
       <c r="AR7" t="n">
         <v>9</v>
@@ -1703,16 +1770,16 @@
         <v>28</v>
       </c>
       <c r="AV7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW7" t="n">
         <v>17</v>
       </c>
       <c r="AX7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ7" t="n">
         <v>6</v>
@@ -1721,10 +1788,10 @@
         <v>23</v>
       </c>
       <c r="BB7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-16-2013-14</t>
+          <t>2013-12-16</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>1.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AE8" t="n">
         <v>8</v>
@@ -1861,13 +1928,13 @@
         <v>9</v>
       </c>
       <c r="AN8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO8" t="n">
         <v>18</v>
       </c>
       <c r="AP8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ8" t="n">
         <v>3</v>
@@ -1876,7 +1943,7 @@
         <v>25</v>
       </c>
       <c r="AS8" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AT8" t="n">
         <v>25</v>
@@ -1885,25 +1952,25 @@
         <v>9</v>
       </c>
       <c r="AV8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW8" t="n">
         <v>4</v>
       </c>
       <c r="AX8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY8" t="n">
         <v>5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA8" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BB8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC8" t="n">
         <v>12</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-16-2013-14</t>
+          <t>2013-12-16</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>2.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AE9" t="n">
         <v>8</v>
@@ -2034,16 +2101,16 @@
         <v>7</v>
       </c>
       <c r="AK9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL9" t="n">
         <v>14</v>
       </c>
       <c r="AM9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO9" t="n">
         <v>12</v>
@@ -2052,13 +2119,13 @@
         <v>7</v>
       </c>
       <c r="AQ9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR9" t="n">
         <v>5</v>
       </c>
       <c r="AS9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT9" t="n">
         <v>3</v>
@@ -2067,7 +2134,7 @@
         <v>14</v>
       </c>
       <c r="AV9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AW9" t="n">
         <v>21</v>
@@ -2076,7 +2143,7 @@
         <v>5</v>
       </c>
       <c r="AY9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ9" t="n">
         <v>22</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-16-2013-14</t>
+          <t>2013-12-16</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F10" t="n">
         <v>14</v>
       </c>
       <c r="G10" t="n">
-        <v>0.462</v>
+        <v>0.44</v>
       </c>
       <c r="H10" t="n">
         <v>48.6</v>
@@ -2135,10 +2202,10 @@
         <v>38.4</v>
       </c>
       <c r="J10" t="n">
-        <v>85.09999999999999</v>
+        <v>85</v>
       </c>
       <c r="K10" t="n">
-        <v>0.451</v>
+        <v>0.452</v>
       </c>
       <c r="L10" t="n">
         <v>6.1</v>
@@ -2147,37 +2214,37 @@
         <v>19.6</v>
       </c>
       <c r="N10" t="n">
-        <v>0.312</v>
+        <v>0.31</v>
       </c>
       <c r="O10" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P10" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.671</v>
+        <v>0.672</v>
       </c>
       <c r="R10" t="n">
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="S10" t="n">
-        <v>30.6</v>
+        <v>30.4</v>
       </c>
       <c r="T10" t="n">
-        <v>44.8</v>
+        <v>44.4</v>
       </c>
       <c r="U10" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="V10" t="n">
-        <v>15.4</v>
+        <v>15.7</v>
       </c>
       <c r="W10" t="n">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="X10" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y10" t="n">
         <v>4.7</v>
@@ -2189,34 +2256,34 @@
         <v>20.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.9</v>
+        <v>-1.2</v>
       </c>
       <c r="AD10" t="n">
         <v>2</v>
       </c>
       <c r="AE10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ10" t="n">
         <v>6</v>
       </c>
       <c r="AK10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL10" t="n">
         <v>26</v>
@@ -2246,28 +2313,28 @@
         <v>9</v>
       </c>
       <c r="AU10" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AV10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AW10" t="n">
         <v>5</v>
       </c>
       <c r="AX10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AZ10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA10" t="n">
         <v>16</v>
       </c>
       <c r="BB10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC10" t="n">
         <v>17</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-16-2013-14</t>
+          <t>2013-12-16</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>2.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="n">
         <v>11</v>
@@ -2392,13 +2459,13 @@
         <v>15</v>
       </c>
       <c r="AI11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ11" t="n">
         <v>16</v>
       </c>
       <c r="AK11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL11" t="n">
         <v>3</v>
@@ -2416,7 +2483,7 @@
         <v>15</v>
       </c>
       <c r="AQ11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR11" t="n">
         <v>20</v>
@@ -2425,7 +2492,7 @@
         <v>3</v>
       </c>
       <c r="AT11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU11" t="n">
         <v>12</v>
@@ -2437,10 +2504,10 @@
         <v>18</v>
       </c>
       <c r="AX11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ11" t="n">
         <v>29</v>
@@ -2449,7 +2516,7 @@
         <v>17</v>
       </c>
       <c r="BB11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC11" t="n">
         <v>9</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-16-2013-14</t>
+          <t>2013-12-16</t>
         </is>
       </c>
     </row>
@@ -2559,22 +2626,22 @@
         <v>4.8</v>
       </c>
       <c r="AD12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE12" t="n">
         <v>6</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>7</v>
       </c>
       <c r="AF12" t="n">
         <v>6</v>
       </c>
       <c r="AG12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ12" t="n">
         <v>28</v>
@@ -2589,7 +2656,7 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO12" t="n">
         <v>1</v>
@@ -2634,7 +2701,7 @@
         <v>2</v>
       </c>
       <c r="BC12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-16-2013-14</t>
+          <t>2013-12-16</t>
         </is>
       </c>
     </row>
@@ -2663,85 +2730,85 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E13" t="n">
         <v>20</v>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>0.833</v>
+        <v>0.87</v>
       </c>
       <c r="H13" t="n">
         <v>48.2</v>
       </c>
       <c r="I13" t="n">
-        <v>36</v>
+        <v>36.1</v>
       </c>
       <c r="J13" t="n">
         <v>79.5</v>
       </c>
       <c r="K13" t="n">
-        <v>0.453</v>
+        <v>0.454</v>
       </c>
       <c r="L13" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M13" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="N13" t="n">
         <v>0.363</v>
       </c>
       <c r="O13" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="P13" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.784</v>
+        <v>0.786</v>
       </c>
       <c r="R13" t="n">
         <v>9.9</v>
       </c>
       <c r="S13" t="n">
-        <v>34.1</v>
+        <v>34.3</v>
       </c>
       <c r="T13" t="n">
-        <v>44</v>
+        <v>44.2</v>
       </c>
       <c r="U13" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="V13" t="n">
-        <v>15.4</v>
+        <v>15.7</v>
       </c>
       <c r="W13" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X13" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z13" t="n">
         <v>19.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>97.7</v>
+        <v>97.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AD13" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AE13" t="n">
         <v>2</v>
@@ -2750,10 +2817,10 @@
         <v>1</v>
       </c>
       <c r="AG13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI13" t="n">
         <v>22</v>
@@ -2765,13 +2832,13 @@
         <v>11</v>
       </c>
       <c r="AL13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM13" t="n">
         <v>19</v>
       </c>
       <c r="AN13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO13" t="n">
         <v>11</v>
@@ -2780,7 +2847,7 @@
         <v>12</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR13" t="n">
         <v>26</v>
@@ -2792,25 +2859,25 @@
         <v>10</v>
       </c>
       <c r="AU13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV13" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AW13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY13" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ13" t="n">
         <v>8</v>
       </c>
       <c r="BA13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB13" t="n">
         <v>20</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-16-2013-14</t>
+          <t>2013-12-16</t>
         </is>
       </c>
     </row>
@@ -2845,82 +2912,82 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F14" t="n">
         <v>9</v>
       </c>
       <c r="G14" t="n">
-        <v>0.654</v>
+        <v>0.64</v>
       </c>
       <c r="H14" t="n">
         <v>48.2</v>
       </c>
       <c r="I14" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J14" t="n">
-        <v>80.8</v>
+        <v>81</v>
       </c>
       <c r="K14" t="n">
-        <v>0.466</v>
+        <v>0.464</v>
       </c>
       <c r="L14" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="M14" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0.335</v>
+        <v>0.329</v>
       </c>
       <c r="O14" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="P14" t="n">
-        <v>29.3</v>
+        <v>29.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.71</v>
+        <v>0.709</v>
       </c>
       <c r="R14" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="S14" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="T14" t="n">
         <v>42.6</v>
       </c>
       <c r="U14" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="V14" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="W14" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X14" t="n">
         <v>4.3</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>104.1</v>
+        <v>103.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="AD14" t="n">
         <v>2</v>
@@ -2938,13 +3005,13 @@
         <v>23</v>
       </c>
       <c r="AI14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ14" t="n">
         <v>24</v>
       </c>
       <c r="AK14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AL14" t="n">
         <v>13</v>
@@ -2953,7 +3020,7 @@
         <v>7</v>
       </c>
       <c r="AN14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AO14" t="n">
         <v>4</v>
@@ -2962,7 +3029,7 @@
         <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR14" t="n">
         <v>23</v>
@@ -2974,22 +3041,22 @@
         <v>17</v>
       </c>
       <c r="AU14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY14" t="n">
         <v>2</v>
       </c>
       <c r="AZ14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA14" t="n">
         <v>2</v>
@@ -2998,7 +3065,7 @@
         <v>5</v>
       </c>
       <c r="BC14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-16-2013-14</t>
+          <t>2013-12-16</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E15" t="n">
         <v>11</v>
       </c>
       <c r="F15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G15" t="n">
-        <v>0.458</v>
+        <v>0.478</v>
       </c>
       <c r="H15" t="n">
         <v>48</v>
@@ -3045,76 +3112,76 @@
         <v>37.5</v>
       </c>
       <c r="J15" t="n">
-        <v>85.09999999999999</v>
+        <v>85.3</v>
       </c>
       <c r="K15" t="n">
-        <v>0.441</v>
+        <v>0.44</v>
       </c>
       <c r="L15" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="M15" t="n">
-        <v>25.5</v>
+        <v>25.7</v>
       </c>
       <c r="N15" t="n">
-        <v>0.386</v>
+        <v>0.391</v>
       </c>
       <c r="O15" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="P15" t="n">
         <v>21.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.735</v>
+        <v>0.732</v>
       </c>
       <c r="R15" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="S15" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="T15" t="n">
         <v>42.8</v>
       </c>
       <c r="U15" t="n">
-        <v>23.5</v>
+        <v>23.7</v>
       </c>
       <c r="V15" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W15" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="X15" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Y15" t="n">
         <v>4.7</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="AA15" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AB15" t="n">
         <v>100.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>-3.4</v>
+        <v>-3</v>
       </c>
       <c r="AD15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF15" t="n">
         <v>12</v>
       </c>
-      <c r="AE15" t="n">
-        <v>16</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>14</v>
-      </c>
       <c r="AG15" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AH15" t="n">
         <v>24</v>
@@ -3126,55 +3193,55 @@
         <v>5</v>
       </c>
       <c r="AK15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM15" t="n">
         <v>2</v>
       </c>
       <c r="AN15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AO15" t="n">
         <v>26</v>
       </c>
       <c r="AP15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR15" t="n">
         <v>22</v>
       </c>
-      <c r="AR15" t="n">
-        <v>21</v>
-      </c>
       <c r="AS15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AV15" t="n">
         <v>14</v>
       </c>
       <c r="AW15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA15" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BB15" t="n">
         <v>14</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-16-2013-14</t>
+          <t>2013-12-16</t>
         </is>
       </c>
     </row>
@@ -3287,13 +3354,13 @@
         <v>-3.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AE16" t="n">
         <v>18</v>
       </c>
       <c r="AF16" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AG16" t="n">
         <v>18</v>
@@ -3317,25 +3384,25 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO16" t="n">
         <v>20</v>
       </c>
       <c r="AP16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ16" t="n">
         <v>12</v>
       </c>
       <c r="AR16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS16" t="n">
         <v>24</v>
       </c>
       <c r="AT16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU16" t="n">
         <v>16</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-16-2013-14</t>
+          <t>2013-12-16</t>
         </is>
       </c>
     </row>
@@ -3391,58 +3458,58 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F17" t="n">
         <v>6</v>
       </c>
       <c r="G17" t="n">
-        <v>0.75</v>
+        <v>0.739</v>
       </c>
       <c r="H17" t="n">
         <v>48</v>
       </c>
       <c r="I17" t="n">
-        <v>38.4</v>
+        <v>38.1</v>
       </c>
       <c r="J17" t="n">
-        <v>75.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="K17" t="n">
-        <v>0.511</v>
+        <v>0.506</v>
       </c>
       <c r="L17" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>21</v>
+        <v>21.3</v>
       </c>
       <c r="N17" t="n">
         <v>0.386</v>
       </c>
       <c r="O17" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="P17" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.763</v>
+        <v>0.761</v>
       </c>
       <c r="R17" t="n">
         <v>6.5</v>
       </c>
       <c r="S17" t="n">
-        <v>29.4</v>
+        <v>29.2</v>
       </c>
       <c r="T17" t="n">
-        <v>35.9</v>
+        <v>35.7</v>
       </c>
       <c r="U17" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="V17" t="n">
         <v>15.7</v>
@@ -3451,25 +3518,25 @@
         <v>9.5</v>
       </c>
       <c r="X17" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y17" t="n">
         <v>2.7</v>
       </c>
       <c r="Z17" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="AA17" t="n">
         <v>21.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>103.7</v>
+        <v>103.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="AD17" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AE17" t="n">
         <v>5</v>
@@ -3484,7 +3551,7 @@
         <v>24</v>
       </c>
       <c r="AI17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3493,22 +3560,22 @@
         <v>1</v>
       </c>
       <c r="AL17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO17" t="n">
         <v>8</v>
       </c>
       <c r="AP17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
@@ -3520,7 +3587,7 @@
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV17" t="n">
         <v>18</v>
@@ -3535,16 +3602,16 @@
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="BA17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-16-2013-14</t>
+          <t>2013-12-16</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3718,13 @@
         <v>-8.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
       </c>
       <c r="AF18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG18" t="n">
         <v>30</v>
@@ -3675,16 +3742,16 @@
         <v>29</v>
       </c>
       <c r="AL18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AM18" t="n">
         <v>22</v>
       </c>
-      <c r="AM18" t="n">
-        <v>23</v>
-      </c>
       <c r="AN18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP18" t="n">
         <v>28</v>
@@ -3693,7 +3760,7 @@
         <v>10</v>
       </c>
       <c r="AR18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS18" t="n">
         <v>28</v>
@@ -3705,16 +3772,16 @@
         <v>19</v>
       </c>
       <c r="AV18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX18" t="n">
         <v>7</v>
       </c>
       <c r="AY18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ18" t="n">
         <v>11</v>
@@ -3726,7 +3793,7 @@
         <v>30</v>
       </c>
       <c r="BC18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-16-2013-14</t>
+          <t>2013-12-16</t>
         </is>
       </c>
     </row>
@@ -3755,100 +3822,100 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E19" t="n">
         <v>12</v>
       </c>
       <c r="F19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G19" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
       </c>
       <c r="I19" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="J19" t="n">
-        <v>89.2</v>
+        <v>88.8</v>
       </c>
       <c r="K19" t="n">
-        <v>0.423</v>
+        <v>0.425</v>
       </c>
       <c r="L19" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0.339</v>
+        <v>0.342</v>
       </c>
       <c r="O19" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="P19" t="n">
         <v>27</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.799</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="R19" t="n">
-        <v>13.4</v>
+        <v>13.2</v>
       </c>
       <c r="S19" t="n">
         <v>31.9</v>
       </c>
       <c r="T19" t="n">
-        <v>45.4</v>
+        <v>45.1</v>
       </c>
       <c r="U19" t="n">
         <v>23</v>
       </c>
       <c r="V19" t="n">
-        <v>14.1</v>
+        <v>14.4</v>
       </c>
       <c r="W19" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Y19" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Z19" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>105.2</v>
+        <v>105.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AE19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF19" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG19" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AH19" t="n">
         <v>21</v>
       </c>
       <c r="AI19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ19" t="n">
         <v>1</v>
@@ -3857,13 +3924,13 @@
         <v>27</v>
       </c>
       <c r="AL19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AM19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO19" t="n">
         <v>3</v>
@@ -3875,10 +3942,10 @@
         <v>4</v>
       </c>
       <c r="AR19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT19" t="n">
         <v>6</v>
@@ -3887,7 +3954,7 @@
         <v>8</v>
       </c>
       <c r="AV19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AW19" t="n">
         <v>2</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-16-2013-14</t>
+          <t>2013-12-16</t>
         </is>
       </c>
     </row>
@@ -4015,16 +4082,16 @@
         <v>0.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE20" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AF20" t="n">
         <v>11</v>
       </c>
       <c r="AG20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH20" t="n">
         <v>3</v>
@@ -4036,16 +4103,16 @@
         <v>3</v>
       </c>
       <c r="AK20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM20" t="n">
         <v>27</v>
       </c>
       <c r="AN20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO20" t="n">
         <v>13</v>
@@ -4057,13 +4124,13 @@
         <v>11</v>
       </c>
       <c r="AR20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS20" t="n">
         <v>26</v>
       </c>
       <c r="AT20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU20" t="n">
         <v>11</v>
@@ -4087,7 +4154,7 @@
         <v>18</v>
       </c>
       <c r="BB20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC20" t="n">
         <v>13</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-16-2013-14</t>
+          <t>2013-12-16</t>
         </is>
       </c>
     </row>
@@ -4119,103 +4186,103 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E21" t="n">
         <v>7</v>
       </c>
       <c r="F21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G21" t="n">
-        <v>0.292</v>
+        <v>0.304</v>
       </c>
       <c r="H21" t="n">
         <v>48.2</v>
       </c>
       <c r="I21" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="J21" t="n">
-        <v>83</v>
+        <v>83.2</v>
       </c>
       <c r="K21" t="n">
-        <v>0.432</v>
+        <v>0.433</v>
       </c>
       <c r="L21" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="M21" t="n">
-        <v>25</v>
+        <v>24.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0.346</v>
+        <v>0.345</v>
       </c>
       <c r="O21" t="n">
-        <v>14</v>
+        <v>13.6</v>
       </c>
       <c r="P21" t="n">
-        <v>18</v>
+        <v>17.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.782</v>
+        <v>0.783</v>
       </c>
       <c r="R21" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="S21" t="n">
-        <v>27.9</v>
+        <v>28</v>
       </c>
       <c r="T21" t="n">
-        <v>38.5</v>
+        <v>38.7</v>
       </c>
       <c r="U21" t="n">
         <v>19.9</v>
       </c>
       <c r="V21" t="n">
-        <v>12.5</v>
+        <v>12.7</v>
       </c>
       <c r="W21" t="n">
         <v>8.6</v>
       </c>
       <c r="X21" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y21" t="n">
         <v>4</v>
       </c>
       <c r="Z21" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>19</v>
+        <v>18.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>94.5</v>
+        <v>94.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>-3.5</v>
+        <v>-3.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AE21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF21" t="n">
         <v>26</v>
       </c>
       <c r="AG21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI21" t="n">
         <v>23</v>
       </c>
       <c r="AJ21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK21" t="n">
         <v>25</v>
@@ -4236,10 +4303,10 @@
         <v>29</v>
       </c>
       <c r="AQ21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS21" t="n">
         <v>30</v>
@@ -4248,7 +4315,7 @@
         <v>29</v>
       </c>
       <c r="AU21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV21" t="n">
         <v>1</v>
@@ -4257,19 +4324,19 @@
         <v>7</v>
       </c>
       <c r="AX21" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AY21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ21" t="n">
         <v>25</v>
       </c>
       <c r="BA21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC21" t="n">
         <v>23</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-16-2013-14</t>
+          <t>2013-12-16</t>
         </is>
       </c>
     </row>
@@ -4379,13 +4446,13 @@
         <v>7</v>
       </c>
       <c r="AD22" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
       </c>
       <c r="AF22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
         <v>3</v>
@@ -4397,7 +4464,7 @@
         <v>6</v>
       </c>
       <c r="AJ22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK22" t="n">
         <v>4</v>
@@ -4406,10 +4473,10 @@
         <v>25</v>
       </c>
       <c r="AM22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AN22" t="n">
         <v>24</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>25</v>
       </c>
       <c r="AO22" t="n">
         <v>2</v>
@@ -4433,13 +4500,13 @@
         <v>13</v>
       </c>
       <c r="AV22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-16-2013-14</t>
+          <t>2013-12-16</t>
         </is>
       </c>
     </row>
@@ -4483,43 +4550,43 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F23" t="n">
         <v>17</v>
       </c>
       <c r="G23" t="n">
-        <v>0.32</v>
+        <v>0.292</v>
       </c>
       <c r="H23" t="n">
         <v>48.6</v>
       </c>
       <c r="I23" t="n">
-        <v>36.8</v>
+        <v>37</v>
       </c>
       <c r="J23" t="n">
         <v>82.2</v>
       </c>
       <c r="K23" t="n">
-        <v>0.448</v>
+        <v>0.45</v>
       </c>
       <c r="L23" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="M23" t="n">
-        <v>21.3</v>
+        <v>21.7</v>
       </c>
       <c r="N23" t="n">
-        <v>0.355</v>
+        <v>0.354</v>
       </c>
       <c r="O23" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="P23" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="Q23" t="n">
         <v>0.759</v>
@@ -4528,19 +4595,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>33.2</v>
+        <v>32.7</v>
       </c>
       <c r="T23" t="n">
-        <v>42.3</v>
+        <v>41.8</v>
       </c>
       <c r="U23" t="n">
         <v>20.4</v>
       </c>
       <c r="V23" t="n">
-        <v>15.9</v>
+        <v>16.1</v>
       </c>
       <c r="W23" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="X23" t="n">
         <v>4.5</v>
@@ -4552,28 +4619,28 @@
         <v>20.6</v>
       </c>
       <c r="AA23" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="AB23" t="n">
-        <v>97</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>-4.2</v>
+        <v>-4.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AE23" t="n">
         <v>25</v>
       </c>
       <c r="AF23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG23" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AH23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI23" t="n">
         <v>18</v>
@@ -4582,16 +4649,16 @@
         <v>17</v>
       </c>
       <c r="AK23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL23" t="n">
         <v>15</v>
       </c>
       <c r="AM23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO23" t="n">
         <v>24</v>
@@ -4600,7 +4667,7 @@
         <v>25</v>
       </c>
       <c r="AQ23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR23" t="n">
         <v>27</v>
@@ -4609,10 +4676,10 @@
         <v>9</v>
       </c>
       <c r="AT23" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AU23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV23" t="n">
         <v>23</v>
@@ -4621,16 +4688,16 @@
         <v>16</v>
       </c>
       <c r="AX23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY23" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AZ23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA23" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BB23" t="n">
         <v>21</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-16-2013-14</t>
+          <t>2013-12-16</t>
         </is>
       </c>
     </row>
@@ -4665,88 +4732,88 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E24" t="n">
         <v>7</v>
       </c>
       <c r="F24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G24" t="n">
-        <v>0.269</v>
+        <v>0.28</v>
       </c>
       <c r="H24" t="n">
         <v>49.2</v>
       </c>
       <c r="I24" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="J24" t="n">
-        <v>88.2</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>0.445</v>
+        <v>0.446</v>
       </c>
       <c r="L24" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="M24" t="n">
-        <v>22.4</v>
+        <v>22.1</v>
       </c>
       <c r="N24" t="n">
-        <v>0.325</v>
+        <v>0.328</v>
       </c>
       <c r="O24" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="P24" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.703</v>
+        <v>0.707</v>
       </c>
       <c r="R24" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="S24" t="n">
-        <v>33.3</v>
+        <v>33.4</v>
       </c>
       <c r="T24" t="n">
-        <v>44.9</v>
+        <v>45.1</v>
       </c>
       <c r="U24" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="V24" t="n">
         <v>17.9</v>
       </c>
       <c r="W24" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X24" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="Y24" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="Z24" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AA24" t="n">
         <v>19.9</v>
       </c>
       <c r="AB24" t="n">
-        <v>101.6</v>
+        <v>101.9</v>
       </c>
       <c r="AC24" t="n">
-        <v>-9.6</v>
+        <v>-8.6</v>
       </c>
       <c r="AD24" t="n">
         <v>2</v>
       </c>
       <c r="AE24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF24" t="n">
         <v>28</v>
@@ -4767,7 +4834,7 @@
         <v>18</v>
       </c>
       <c r="AL24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AM24" t="n">
         <v>11</v>
@@ -4776,7 +4843,7 @@
         <v>27</v>
       </c>
       <c r="AO24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP24" t="n">
         <v>17</v>
@@ -4788,10 +4855,10 @@
         <v>10</v>
       </c>
       <c r="AS24" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT24" t="n">
         <v>7</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>8</v>
       </c>
       <c r="AU24" t="n">
         <v>10</v>
@@ -4800,16 +4867,16 @@
         <v>30</v>
       </c>
       <c r="AW24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX24" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AY24" t="n">
         <v>29</v>
       </c>
       <c r="AZ24" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA24" t="n">
         <v>20</v>
@@ -4818,7 +4885,7 @@
         <v>13</v>
       </c>
       <c r="BC24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-16-2013-14</t>
+          <t>2013-12-16</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>2.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AE25" t="n">
         <v>8</v>
@@ -4943,10 +5010,10 @@
         <v>11</v>
       </c>
       <c r="AJ25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL25" t="n">
         <v>5</v>
@@ -4967,22 +5034,22 @@
         <v>21</v>
       </c>
       <c r="AR25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS25" t="n">
         <v>17</v>
       </c>
-      <c r="AS25" t="n">
-        <v>18</v>
-      </c>
       <c r="AT25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU25" t="n">
         <v>27</v>
       </c>
       <c r="AV25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX25" t="n">
         <v>12</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-16-2013-14</t>
+          <t>2013-12-16</t>
         </is>
       </c>
     </row>
@@ -5107,16 +5174,16 @@
         <v>7.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
       </c>
       <c r="AF26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH26" t="n">
         <v>15</v>
@@ -5131,10 +5198,10 @@
         <v>9</v>
       </c>
       <c r="AL26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN26" t="n">
         <v>2</v>
@@ -5152,16 +5219,16 @@
         <v>4</v>
       </c>
       <c r="AS26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT26" t="n">
         <v>5</v>
       </c>
       <c r="AU26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AV26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW26" t="n">
         <v>30</v>
@@ -5182,7 +5249,7 @@
         <v>1</v>
       </c>
       <c r="BC26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-16-2013-14</t>
+          <t>2013-12-16</t>
         </is>
       </c>
     </row>
@@ -5289,16 +5356,16 @@
         <v>-2.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF27" t="n">
         <v>24</v>
       </c>
       <c r="AG27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH27" t="n">
         <v>11</v>
@@ -5307,25 +5374,25 @@
         <v>19</v>
       </c>
       <c r="AJ27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK27" t="n">
         <v>22</v>
       </c>
       <c r="AL27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AN27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO27" t="n">
         <v>7</v>
       </c>
       <c r="AP27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ27" t="n">
         <v>5</v>
@@ -5334,19 +5401,19 @@
         <v>11</v>
       </c>
       <c r="AS27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT27" t="n">
         <v>18</v>
       </c>
       <c r="AU27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV27" t="n">
         <v>5</v>
       </c>
       <c r="AW27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX27" t="n">
         <v>29</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-16-2013-14</t>
+          <t>2013-12-16</t>
         </is>
       </c>
     </row>
@@ -5393,94 +5460,94 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E28" t="n">
         <v>19</v>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
-        <v>0.792</v>
+        <v>0.826</v>
       </c>
       <c r="H28" t="n">
         <v>48</v>
       </c>
       <c r="I28" t="n">
-        <v>41.2</v>
+        <v>41.4</v>
       </c>
       <c r="J28" t="n">
-        <v>83.40000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="K28" t="n">
         <v>0.494</v>
       </c>
       <c r="L28" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="M28" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="N28" t="n">
-        <v>0.4</v>
+        <v>0.402</v>
       </c>
       <c r="O28" t="n">
         <v>12.2</v>
       </c>
       <c r="P28" t="n">
-        <v>16.3</v>
+        <v>16</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.749</v>
+        <v>0.759</v>
       </c>
       <c r="R28" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S28" t="n">
-        <v>33.9</v>
+        <v>34.2</v>
       </c>
       <c r="T28" t="n">
-        <v>42.7</v>
+        <v>43</v>
       </c>
       <c r="U28" t="n">
-        <v>25.1</v>
+        <v>25.3</v>
       </c>
       <c r="V28" t="n">
-        <v>14.8</v>
+        <v>14.5</v>
       </c>
       <c r="W28" t="n">
         <v>8</v>
       </c>
       <c r="X28" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y28" t="n">
         <v>4.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.7</v>
+        <v>17.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>102.9</v>
+        <v>103.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.800000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AE28" t="n">
         <v>3</v>
       </c>
       <c r="AF28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH28" t="n">
         <v>24</v>
@@ -5495,10 +5562,10 @@
         <v>2</v>
       </c>
       <c r="AL28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AM28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN28" t="n">
         <v>3</v>
@@ -5510,22 +5577,22 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR28" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS28" t="n">
         <v>5</v>
       </c>
       <c r="AT28" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AU28" t="n">
         <v>1</v>
       </c>
       <c r="AV28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AW28" t="n">
         <v>15</v>
@@ -5534,7 +5601,7 @@
         <v>22</v>
       </c>
       <c r="AY28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ28" t="n">
         <v>2</v>
@@ -5543,7 +5610,7 @@
         <v>30</v>
       </c>
       <c r="BB28" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BC28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-16-2013-14</t>
+          <t>2013-12-16</t>
         </is>
       </c>
     </row>
@@ -5653,16 +5720,16 @@
         <v>0.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF29" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AG29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH29" t="n">
         <v>5</v>
@@ -5674,16 +5741,16 @@
         <v>15</v>
       </c>
       <c r="AK29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL29" t="n">
         <v>16</v>
       </c>
       <c r="AM29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AN29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO29" t="n">
         <v>6</v>
@@ -5692,7 +5759,7 @@
         <v>9</v>
       </c>
       <c r="AQ29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR29" t="n">
         <v>7</v>
@@ -5719,16 +5786,16 @@
         <v>20</v>
       </c>
       <c r="AZ29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB29" t="n">
         <v>18</v>
       </c>
       <c r="BC29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-16-2013-14</t>
+          <t>2013-12-16</t>
         </is>
       </c>
     </row>
@@ -5757,28 +5824,28 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E30" t="n">
         <v>6</v>
       </c>
       <c r="F30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G30" t="n">
-        <v>0.222</v>
+        <v>0.231</v>
       </c>
       <c r="H30" t="n">
         <v>48.4</v>
       </c>
       <c r="I30" t="n">
-        <v>35.6</v>
+        <v>35.5</v>
       </c>
       <c r="J30" t="n">
-        <v>81.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="K30" t="n">
-        <v>0.434</v>
+        <v>0.433</v>
       </c>
       <c r="L30" t="n">
         <v>6</v>
@@ -5787,28 +5854,28 @@
         <v>17.7</v>
       </c>
       <c r="N30" t="n">
-        <v>0.337</v>
+        <v>0.339</v>
       </c>
       <c r="O30" t="n">
-        <v>16.2</v>
+        <v>16.4</v>
       </c>
       <c r="P30" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.746</v>
+        <v>0.749</v>
       </c>
       <c r="R30" t="n">
         <v>11.9</v>
       </c>
       <c r="S30" t="n">
-        <v>28.7</v>
+        <v>29</v>
       </c>
       <c r="T30" t="n">
-        <v>40.6</v>
+        <v>40.9</v>
       </c>
       <c r="U30" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="V30" t="n">
         <v>15.7</v>
@@ -5817,22 +5884,22 @@
         <v>7.2</v>
       </c>
       <c r="X30" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Z30" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AA30" t="n">
-        <v>21.1</v>
+        <v>21.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>93.40000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="AC30" t="n">
-        <v>-8.800000000000001</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="AD30" t="n">
         <v>1</v>
@@ -5853,10 +5920,10 @@
         <v>26</v>
       </c>
       <c r="AJ30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL30" t="n">
         <v>27</v>
@@ -5865,7 +5932,7 @@
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO30" t="n">
         <v>19</v>
@@ -5874,7 +5941,7 @@
         <v>19</v>
       </c>
       <c r="AQ30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR30" t="n">
         <v>8</v>
@@ -5883,28 +5950,28 @@
         <v>29</v>
       </c>
       <c r="AT30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX30" t="n">
         <v>15</v>
       </c>
       <c r="AY30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ30" t="n">
         <v>23</v>
       </c>
       <c r="BA30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB30" t="n">
         <v>27</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-16-2013-14</t>
+          <t>2013-12-16</t>
         </is>
       </c>
     </row>
@@ -5939,148 +6006,148 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F31" t="n">
         <v>13</v>
       </c>
       <c r="G31" t="n">
-        <v>0.435</v>
+        <v>0.409</v>
       </c>
       <c r="H31" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
       <c r="I31" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J31" t="n">
-        <v>83.8</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.445</v>
+        <v>0.441</v>
       </c>
       <c r="L31" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M31" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="N31" t="n">
-        <v>0.384</v>
+        <v>0.376</v>
       </c>
       <c r="O31" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="P31" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.731</v>
+        <v>0.73</v>
       </c>
       <c r="R31" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="S31" t="n">
-        <v>31.4</v>
+        <v>31.2</v>
       </c>
       <c r="T31" t="n">
         <v>42</v>
       </c>
       <c r="U31" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="V31" t="n">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
       <c r="W31" t="n">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="X31" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y31" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Z31" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="AA31" t="n">
         <v>19.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>98.3</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>-1.4</v>
+        <v>-1.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AE31" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AF31" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AG31" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AH31" t="n">
         <v>1</v>
       </c>
       <c r="AI31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ31" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AK31" t="n">
         <v>19</v>
       </c>
       <c r="AL31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM31" t="n">
         <v>12</v>
       </c>
       <c r="AN31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ31" t="n">
         <v>24</v>
       </c>
       <c r="AR31" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT31" t="n">
         <v>19</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>17</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>20</v>
       </c>
       <c r="AU31" t="n">
         <v>7</v>
       </c>
       <c r="AV31" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AW31" t="n">
         <v>6</v>
       </c>
       <c r="AX31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ31" t="n">
         <v>7</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-16-2013-14</t>
+          <t>2013-12-16</t>
         </is>
       </c>
     </row>
